--- a/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
+++ b/InputData/trans/BSfVBP/BAU Subsidy for Vehicle Battery Production.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BSfVBP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\trans\BSfVBP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D16806-131B-4A2F-BC1B-5BA65B276163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A610ACD6-85CD-4836-81C7-2EC9458F9CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Sources:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Price</t>
   </si>
@@ -51,33 +48,18 @@
     <t>BSfVBP BAU Subsidy for Vehicle Battery Production</t>
   </si>
   <si>
-    <t>2022 to 2012 USD</t>
-  </si>
-  <si>
-    <t>In the US, the Inflation Reduction Act includes a credit of $35/kWh for battery cells and $10/kWh for assembly for onroad vehicle</t>
-  </si>
-  <si>
-    <t>batteries.</t>
-  </si>
-  <si>
-    <t>United States Congress</t>
-  </si>
-  <si>
-    <t>H.R. 5376 - Inflation Reduction Act of 2022</t>
-  </si>
-  <si>
-    <t>https://www.congress.gov/bill/117th-congress/house-bill/5376/text</t>
+    <t>Currently, South Korea does not implement a direct subsidy program for electric vehicle battery manufacturers similar to the Inflation Reduction Act (IRA) in the United States. Instead, the government provides subsidies to electric vehicle buyers to promote the adoption of EVs.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -85,8 +67,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -114,11 +103,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -134,9 +123,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,7 +163,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -280,7 +269,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,7 +411,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -430,64 +419,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="101.28515625" customWidth="1"/>
+    <col min="2" max="2" width="101.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>0.78500000000000003</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -498,11 +452,11 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -595,9 +549,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -606,44 +560,34 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <f>45*About!$A$12</f>
-        <v>35.325000000000003</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>0</v>
@@ -701,6 +645,178 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7BC5186-5AE1-4A45-A346-9E4EC3C5D007}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEF17E49-478F-4678-ABEB-A2EB030497A7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA60CD6B-F898-47A3-AD83-71C124C95B02}"/>
 </file>